--- a/tables/TableS2_HyperTable.xlsx
+++ b/tables/TableS2_HyperTable.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>700</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.7137824375771967</v>
+        <v>0.7114473955732072</v>
       </c>
     </row>
     <row r="11">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01560334402022795</v>
+        <v>0.01441724099585948</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6853932584269663</v>
+        <v>0.6862575626620571</v>
       </c>
     </row>
     <row r="13">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7387543252595156</v>
+        <v>0.7303370786516854</v>
       </c>
     </row>
     <row r="14">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6063303556208186</v>
+        <v>0.6182585764998968</v>
       </c>
     </row>
     <row r="15">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.01101529420814023</v>
+        <v>0.009550488728373359</v>
       </c>
     </row>
     <row r="16">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.5868625756266206</v>
+        <v>0.6032843560933449</v>
       </c>
     </row>
     <row r="17">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.6228373702422145</v>
+        <v>0.6361279170267934</v>
       </c>
     </row>
   </sheetData>
